--- a/docs/E-AUDIT-Rulebook-and-Design.xlsx
+++ b/docs/E-AUDIT-Rulebook-and-Design.xlsx
@@ -752,7 +752,7 @@
       </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>Reachable from the PoC's data model; no reconciling item written yet.</t>
+          <t>Reachable from the PoC's data model; no qualification rule written for it yet.</t>
         </is>
       </c>
       <c r="R5" s="4" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="Q6" s="5" t="inlineStr">
         <is>
-          <t>Reachable from the PoC's data model; no reconciling item written yet.</t>
+          <t>Reachable from the PoC's data model; no qualification rule written for it yet.</t>
         </is>
       </c>
       <c r="R6" s="4" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
-          <t>Reachable from the PoC's data model; no reconciling item written yet.</t>
+          <t>Reachable from the PoC's data model; no qualification rule written for it yet.</t>
         </is>
       </c>
       <c r="R7" s="4" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
-          <t>Draws a live bridge line (app/reconciling_items.py).</t>
+          <t>A qualification rule in app/pipeline/rules.py — it changes the expected return.</t>
         </is>
       </c>
       <c r="R11" s="4" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Q13" s="5" t="inlineStr">
         <is>
-          <t>Reachable from the PoC's data model; no reconciling item written yet.</t>
+          <t>Reachable from the PoC's data model; no qualification rule written for it yet.</t>
         </is>
       </c>
       <c r="R13" s="4" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Q18" s="5" t="inlineStr">
         <is>
-          <t>Reachable from the PoC's data model; no reconciling item written yet.</t>
+          <t>Reachable from the PoC's data model; no qualification rule written for it yet.</t>
         </is>
       </c>
       <c r="R18" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
-          <t>Reachable from the PoC's data model; no reconciling item written yet.</t>
+          <t>Reachable from the PoC's data model; no qualification rule written for it yet.</t>
         </is>
       </c>
       <c r="R19" s="4" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="Q23" s="5" t="inlineStr">
         <is>
-          <t>Draws a live bridge line (app/reconciling_items.py).</t>
+          <t>A qualification rule in app/pipeline/rules.py — it changes the expected return.</t>
         </is>
       </c>
       <c r="R23" s="4" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="Q36" s="5" t="inlineStr">
         <is>
-          <t>Draws a live bridge line (app/reconciling_items.py).</t>
+          <t>A qualification rule in app/pipeline/rules.py — it changes the expected return.</t>
         </is>
       </c>
       <c r="R36" s="4" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="Q37" s="5" t="inlineStr">
         <is>
-          <t>Draws a live bridge line (app/reconciling_items.py).</t>
+          <t>A qualification rule in app/pipeline/rules.py — it changes the expected return.</t>
         </is>
       </c>
       <c r="R37" s="4" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="Q38" s="5" t="inlineStr">
         <is>
-          <t>Reachable from the PoC's data model; no reconciling item written yet.</t>
+          <t>Reachable from the PoC's data model; no qualification rule written for it yet.</t>
         </is>
       </c>
       <c r="R38" s="4" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="Q42" s="5" t="inlineStr">
         <is>
-          <t>Reachable from the PoC's data model; no reconciling item written yet.</t>
+          <t>Reachable from the PoC's data model; no qualification rule written for it yet.</t>
         </is>
       </c>
       <c r="R42" s="4" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="Q46" s="5" t="inlineStr">
         <is>
-          <t>Reachable from the PoC's data model; no reconciling item written yet.</t>
+          <t>Reachable from the PoC's data model; no qualification rule written for it yet.</t>
         </is>
       </c>
       <c r="R46" s="4" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="Q48" s="5" t="inlineStr">
         <is>
-          <t>Reachable from the PoC's data model; no reconciling item written yet.</t>
+          <t>Reachable from the PoC's data model; no qualification rule written for it yet.</t>
         </is>
       </c>
       <c r="R48" s="4" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="Q52" s="5" t="inlineStr">
         <is>
-          <t>Reachable from the PoC's data model; no reconciling item written yet.</t>
+          <t>Reachable from the PoC's data model; no qualification rule written for it yet.</t>
         </is>
       </c>
       <c r="R52" s="4" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="Q53" s="5" t="inlineStr">
         <is>
-          <t>Reachable from the PoC's data model; no reconciling item written yet.</t>
+          <t>Reachable from the PoC's data model; no qualification rule written for it yet.</t>
         </is>
       </c>
       <c r="R53" s="4" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="Q54" s="5" t="inlineStr">
         <is>
-          <t>Reachable from the PoC's data model; no reconciling item written yet.</t>
+          <t>Reachable from the PoC's data model; no qualification rule written for it yet.</t>
         </is>
       </c>
       <c r="R54" s="4" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="Q61" s="5" t="inlineStr">
         <is>
-          <t>Reachable from the PoC's data model; no reconciling item written yet.</t>
+          <t>Reachable from the PoC's data model; no qualification rule written for it yet.</t>
         </is>
       </c>
       <c r="R61" s="4" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="Q62" s="5" t="inlineStr">
         <is>
-          <t>Reachable from the PoC's data model; no reconciling item written yet.</t>
+          <t>Reachable from the PoC's data model; no qualification rule written for it yet.</t>
         </is>
       </c>
       <c r="R62" s="4" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="Q67" s="5" t="inlineStr">
         <is>
-          <t>Reachable from the PoC's data model; no reconciling item written yet.</t>
+          <t>Reachable from the PoC's data model; no qualification rule written for it yet.</t>
         </is>
       </c>
       <c r="R67" s="4" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="Q68" s="5" t="inlineStr">
         <is>
-          <t>Reachable from the PoC's data model; no reconciling item written yet.</t>
+          <t>Reachable from the PoC's data model; no qualification rule written for it yet.</t>
         </is>
       </c>
       <c r="R68" s="4" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="Q69" s="5" t="inlineStr">
         <is>
-          <t>Reachable from the PoC's data model; no reconciling item written yet.</t>
+          <t>Reachable from the PoC's data model; no qualification rule written for it yet.</t>
         </is>
       </c>
       <c r="R69" s="4" t="inlineStr">
@@ -7690,7 +7690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8171,29 +8171,29 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>CASE-2025-0485</t>
+          <t>CASE-2025-0487</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Najd Electronics Trading</t>
+          <t>Hail Medical Supplies Co.</t>
         </is>
       </c>
       <c r="C28" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>0.722</v>
+        <v>0.778</v>
       </c>
       <c r="E28" s="13" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="G28" s="14">
         <f>ROUND((($B$6*C28)+($B$7*D28)+($B$8*E28)+($B$9*F28))*100,0)</f>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H28" s="4" t="str">
         <f>IF(G28&gt;=60,"High",IF(G28&gt;=35,"Medium","Low"))</f>
@@ -8203,83 +8203,83 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>CASE-2025-0486</t>
+          <t>CASE-2025-0485</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Yanbu Petrochem Supplies</t>
+          <t>Najd Electronics Trading</t>
         </is>
       </c>
       <c r="C29" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>0.556</v>
+        <v>0.722</v>
       </c>
       <c r="E29" s="13" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="G29" s="14">
         <f>ROUND((($B$6*C29)+($B$7*D29)+($B$8*E29)+($B$9*F29))*100,0)</f>
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H29" s="4" t="str">
         <f>IF(G29&gt;=60,"High",IF(G29&gt;=35,"Medium","Low"))</f>
-        <v>Medium</v>
+        <v>High</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>CASE-2025-0483</t>
+          <t>CASE-2025-0486</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Rawabi Construction Co.</t>
+          <t>Yanbu Petrochem Supplies</t>
         </is>
       </c>
       <c r="C30" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>0.667</v>
+        <v>0.556</v>
       </c>
       <c r="E30" s="13" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="14">
         <f>ROUND((($B$6*C30)+($B$7*D30)+($B$8*E30)+($B$9*F30))*100,0)</f>
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="H30" s="4" t="str">
         <f>IF(G30&gt;=60,"High",IF(G30&gt;=35,"Medium","Low"))</f>
-        <v>Low</v>
+        <v>Medium</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>CASE-2025-0484</t>
+          <t>CASE-2025-0483</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Tabuk Logistics Co.</t>
+          <t>Rawabi Construction Co.</t>
         </is>
       </c>
       <c r="C31" s="13" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>0.444</v>
+        <v>0.667</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>0</v>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="G31" s="14">
         <f>ROUND((($B$6*C31)+($B$7*D31)+($B$8*E31)+($B$9*F31))*100,0)</f>
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H31" s="4" t="str">
         <f>IF(G31&gt;=60,"High",IF(G31&gt;=35,"Medium","Low"))</f>
@@ -8299,39 +8299,71 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>CASE-2025-0482</t>
+          <t>CASE-2025-0484</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Nael Foodstuff Est.</t>
+          <t>Tabuk Logistics Co.</t>
         </is>
       </c>
       <c r="C32" s="13" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>0.5</v>
+        <v>0.444</v>
       </c>
       <c r="E32" s="13" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="14">
         <f>ROUND((($B$6*C32)+($B$7*D32)+($B$8*E32)+($B$9*F32))*100,0)</f>
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H32" s="4" t="str">
         <f>IF(G32&gt;=60,"High",IF(G32&gt;=35,"Medium","Low"))</f>
         <v>Low</v>
       </c>
     </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>Signal values (blue) are the engine's output for the seeded demo data on 2026-08-15; Score and Band are formulas over the weights in block A. Deadline signals move as the SLA date approaches.</t>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>CASE-2025-0482</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Nael Foodstuff Est.</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <f>ROUND((($B$6*C33)+($B$7*D33)+($B$8*E33)+($B$9*F33))*100,0)</f>
+        <v>15</v>
+      </c>
+      <c r="H33" s="4" t="str">
+        <f>IF(G33&gt;=60,"High",IF(G33&gt;=35,"Medium","Low"))</f>
+        <v>Low</v>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>Signal values (blue) are the engine's output for the seeded demo data on 2026-08-18; Score and Band are formulas over the weights in block A. Deadline signals move as the SLA date approaches.</t>
         </is>
       </c>
     </row>
@@ -8340,10 +8372,10 @@
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="A25:H25"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8355,7 +8387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F150"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8376,7 +8408,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Two PostgreSQL schemas. 'core' holds what the taxpayer declared and what the e-invoices evidence; 'recon' holds the reconciliation working state the engine writes. Row counts are the seeded demo volumes.</t>
+          <t>Two PostgreSQL schemas. 'core' holds what the taxpayer declared and what the e-invoices evidence; 'recon' holds the reconciliation working state the engine writes. Row counts are the seeded demo volumes. Block D is the important one: it is what the engine actually does to each line, in order, before anything is summed.</t>
         </is>
       </c>
     </row>
@@ -8419,7 +8451,7 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="4" t="inlineStr"/>
       <c r="E6" s="4" t="inlineStr"/>
@@ -8437,7 +8469,7 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D7" s="4" t="inlineStr"/>
       <c r="E7" s="4" t="inlineStr"/>
@@ -8455,7 +8487,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D8" s="4" t="inlineStr"/>
       <c r="E8" s="4" t="inlineStr"/>
@@ -8473,7 +8505,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="4" t="inlineStr"/>
@@ -8491,7 +8523,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="D10" s="4" t="inlineStr"/>
       <c r="E10" s="4" t="inlineStr"/>
@@ -8509,7 +8541,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" s="4" t="inlineStr"/>
       <c r="E11" s="4" t="inlineStr"/>
@@ -11105,7 +11137,7 @@
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>D. The selection predicates the engine actually applies (app/recon_engine.py)</t>
+          <t>D. What the engine does to each line, in order (app/pipeline)</t>
         </is>
       </c>
     </row>
@@ -11117,12 +11149,12 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>Predicate</t>
+          <t>Predicate applied</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Why</t>
+          <t>Why it matters</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr"/>
@@ -11132,7 +11164,7 @@
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>Pick the return</t>
+          <t>1. Pick the return</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
@@ -11152,7 +11184,7 @@
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>Pick the declared box</t>
+          <t>2. Pick the declared box</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
@@ -11172,17 +11204,17 @@
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>Select the evidence</t>
+          <t>3. Explode to line grain</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>invoice.taxpayer_id = taxpayer.id AND invoice.direction = 'sale' (or 'purchase') AND invoice.status_code IN ('cleared','reported')</t>
+          <t>one row per invoice_taxsubtotal, joined to its invoice and the case period</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>Rejected and cancelled documents never enter the reconstruction.</t>
+          <t>The unit of computation is the tax-subtotal line, not the invoice and not the box total. Everything below acts on a line.</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr"/>
@@ -11192,17 +11224,17 @@
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>Aggregate the VAT</t>
+          <t>4. Stage: status</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>SUM(invoice_taxsubtotal.tax_amount) WHERE category = 'S' AND rate = 15</t>
+          <t>EXCLUDE WHERE invoice.status_code NOT IN ('cleared','reported')</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>This is the reconstruction. Zero-rated and exempt lines are excluded by the predicate, which is why only the standard-rated box is reconciled.</t>
+          <t>Structural, not a rule. A rejected or cancelled document is not evidence of a supply, so it is not something an auditor may toggle back on.</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr"/>
@@ -11212,17 +11244,17 @@
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>Split the population</t>
+          <t>5. Stage: category</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>invoice_type_code = 381 → credit notes; everything else → reconstructed gross</t>
+          <t>EXCLUDE WHERE category &lt;&gt; 'S' OR rate &lt;&gt; 15</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>Structural, not a rule: a credit note is never part of gross, so disabling COR-01 removes the explanation without restating the reconstruction.</t>
+          <t>This is why only the standard-rated box is reconciled. Zero-rated, exempt and 5% lines leave the population here, explicitly rather than by never being summed.</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr"/>
@@ -11232,17 +11264,17 @@
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>Test the tax point</t>
+          <t>6. Stage: tax point</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>invoice.delivery_date &gt; case.period_to</t>
+          <t>DEFER TO NEXT PERIOD WHERE type_code &lt;&gt; 381 AND delivery_date &gt; case.period_to</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>The period-straddle test behind OUT-07 and INP-09. Delivery date is a proxy for the true tax point.</t>
+          <t>A reassignment, not a subtraction: the supply leaves this period and belongs to the next. This is what a sum-then-adjust design cannot express. Rules OUT-07 / INP-09.</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr"/>
@@ -11252,17 +11284,17 @@
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>Fold in evidence</t>
+          <t>7. Stage: adjustment</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>taxpayer_response.case_id = case.case_id ORDER BY seq</t>
+          <t>ADMIT WHERE type_code = 381 (credit notes carry a negative amount)</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>Each auditor-confirmed response becomes a RESP-xx bridge line.</t>
+          <t>Credit notes are part of the correct sum, not a correction to a finished one. Disabling COR-01 / COR-02 removes them from the reconstruction entirely.</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr"/>
@@ -11272,25 +11304,72 @@
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>Prior findings</t>
+          <t>8. Sum the survivors</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>audit_case.taxpayer_id = case.taxpayer_id AND case_id &lt;&gt; case.case_id AND diff_tax_amt &gt; 0</t>
+          <t>expected_vat = SUM(tax_amount) over lines still admitted in this period</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>The history priority signal.</t>
+          <t>Only now is anything added up. A line is admitted at most once, so two rules cannot double-count the same document.</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr"/>
       <c r="E150" s="4" t="inlineStr"/>
       <c r="F150" s="4" t="inlineStr"/>
     </row>
+    <row r="151">
+      <c r="A151" s="7" t="inlineStr">
+        <is>
+          <t>9. Compare</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>residual = expected_vat + auditor-confirmed responses - declared</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>Taxpayer evidence is not a line decision — it applies after qualification, against the difference that survived.</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr"/>
+      <c r="E151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="7" t="inlineStr">
+        <is>
+          <t>10. Prior findings</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>audit_case.taxpayer_id = case.taxpayer_id AND case_id &lt;&gt; case.case_id AND diff_tax_amt &gt; 0</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>Feeds the history signal in the priority score.</t>
+        </is>
+      </c>
+      <c r="D152" s="4" t="inlineStr"/>
+      <c r="E152" s="4" t="inlineStr"/>
+      <c r="F152" s="4" t="inlineStr"/>
+    </row>
+    <row r="154" ht="42" customHeight="1">
+      <c r="A154" s="15" t="inlineStr">
+        <is>
+          <t>Every decision above is recorded per line, so the bridge is derived from what the rules did rather than hand-written: base + movements = expected holds by construction. Rules are declarative predicates that also render as SQL, so the same registry can drive a set-based batch job at national volumes.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A128:F128"/>
     <mergeCell ref="A1:F1"/>
@@ -11298,6 +11377,7 @@
     <mergeCell ref="A126:F126"/>
     <mergeCell ref="A141:F141"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A154:F154"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
